--- a/output/roomself_excel/13044.xlsx
+++ b/output/roomself_excel/13044.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>432508</v>
+        <v>19680</v>
       </c>
       <c r="D2" t="n">
-        <v>6436</v>
+        <v>1132</v>
       </c>
       <c r="E2" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>170940</v>
+        <v>86655</v>
       </c>
       <c r="D3" t="n">
-        <v>3328</v>
+        <v>2368</v>
       </c>
       <c r="E3" t="n">
-        <v>482</v>
+        <v>347</v>
       </c>
       <c r="F3" t="n">
-        <v>390</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86655</v>
+        <v>231381</v>
       </c>
       <c r="D4" t="n">
-        <v>2368</v>
+        <v>3884</v>
       </c>
       <c r="E4" t="n">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51888</v>
+        <v>171058</v>
       </c>
       <c r="D5" t="n">
-        <v>1856</v>
+        <v>4556</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>127857</v>
+        <v>432508</v>
       </c>
       <c r="D6" t="n">
-        <v>2872</v>
+        <v>6436</v>
       </c>
       <c r="E6" t="n">
-        <v>327</v>
+        <v>1008</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18178</v>
+        <v>170940</v>
       </c>
       <c r="D7" t="n">
-        <v>1084</v>
+        <v>3328</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13420</v>
+        <v>51888</v>
       </c>
       <c r="D8" t="n">
-        <v>928</v>
+        <v>1856</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>129669</v>
+        <v>127857</v>
       </c>
       <c r="D9" t="n">
-        <v>3960</v>
+        <v>2872</v>
       </c>
       <c r="E9" t="n">
-        <v>507</v>
+        <v>327</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>414708</v>
+        <v>18178</v>
       </c>
       <c r="D10" t="n">
-        <v>7800</v>
+        <v>1084</v>
       </c>
       <c r="E10" t="n">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83979</v>
+        <v>13420</v>
       </c>
       <c r="D11" t="n">
-        <v>2320</v>
+        <v>928</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>420876</v>
+        <v>129669</v>
       </c>
       <c r="D12" t="n">
-        <v>5620</v>
+        <v>3960</v>
       </c>
       <c r="E12" t="n">
-        <v>1012</v>
+        <v>507</v>
       </c>
       <c r="F12" t="n">
-        <v>453</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>399492</v>
+        <v>414708</v>
       </c>
       <c r="D13" t="n">
-        <v>5532</v>
+        <v>7800</v>
       </c>
       <c r="E13" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="F13" t="n">
-        <v>411</v>
+        <v>703</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>578592</v>
+        <v>83979</v>
       </c>
       <c r="D14" t="n">
-        <v>7472</v>
+        <v>2320</v>
       </c>
       <c r="E14" t="n">
-        <v>1516</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>278235</v>
+        <v>420876</v>
       </c>
       <c r="D15" t="n">
-        <v>4368</v>
+        <v>5620</v>
       </c>
       <c r="E15" t="n">
-        <v>707</v>
+        <v>1012</v>
       </c>
       <c r="F15" t="n">
-        <v>425</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>129540</v>
+        <v>399492</v>
       </c>
       <c r="D16" t="n">
-        <v>3056</v>
+        <v>5532</v>
       </c>
       <c r="E16" t="n">
-        <v>981</v>
+        <v>1012</v>
       </c>
       <c r="F16" t="n">
-        <v>445</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37583802</v>
+        <v>578592</v>
       </c>
       <c r="D17" t="n">
-        <v>62768</v>
+        <v>7472</v>
       </c>
       <c r="E17" t="n">
-        <v>13426</v>
+        <v>1516</v>
       </c>
       <c r="F17" t="n">
-        <v>3962</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>159194</v>
+        <v>278235</v>
       </c>
       <c r="D18" t="n">
-        <v>3420</v>
+        <v>4368</v>
       </c>
       <c r="E18" t="n">
-        <v>581</v>
+        <v>707</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>196125</v>
+        <v>129540</v>
       </c>
       <c r="D19" t="n">
-        <v>3896</v>
+        <v>3056</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>120904</v>
+        <v>37583802</v>
       </c>
       <c r="D20" t="n">
-        <v>2920</v>
+        <v>62768</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>12425</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25088</v>
+        <v>159194</v>
       </c>
       <c r="D21" t="n">
-        <v>1344</v>
+        <v>3420</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>118752</v>
+        <v>196125</v>
       </c>
       <c r="D22" t="n">
-        <v>3768</v>
+        <v>3896</v>
       </c>
       <c r="E22" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>125904</v>
+        <v>120904</v>
       </c>
       <c r="D23" t="n">
-        <v>3484</v>
+        <v>2920</v>
       </c>
       <c r="E23" t="n">
-        <v>1046</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>661105</v>
+        <v>25088</v>
       </c>
       <c r="D24" t="n">
-        <v>8696</v>
+        <v>1344</v>
       </c>
       <c r="E24" t="n">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19680</v>
+        <v>118752</v>
       </c>
       <c r="D25" t="n">
-        <v>1132</v>
+        <v>3768</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>88524</v>
+        <v>125904</v>
       </c>
       <c r="D26" t="n">
-        <v>2740</v>
+        <v>3484</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18900</v>
+        <v>661105</v>
       </c>
       <c r="D27" t="n">
-        <v>1140</v>
+        <v>8696</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12423</v>
+        <v>88524</v>
       </c>
       <c r="D28" t="n">
-        <v>896</v>
+        <v>2740</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>231928</v>
+        <v>18900</v>
       </c>
       <c r="D29" t="n">
-        <v>3884</v>
+        <v>1140</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>58416</v>
+        <v>12423</v>
       </c>
       <c r="D30" t="n">
-        <v>2956</v>
+        <v>896</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18172</v>
+        <v>547</v>
       </c>
       <c r="D31" t="n">
-        <v>1088</v>
+        <v>1285</v>
       </c>
       <c r="E31" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1126,20 +1126,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>171058</v>
+        <v>58416</v>
       </c>
       <c r="D32" t="n">
-        <v>4556</v>
+        <v>2956</v>
       </c>
       <c r="E32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>91854</v>
+        <v>18172</v>
       </c>
       <c r="D33" t="n">
-        <v>2484</v>
+        <v>1088</v>
       </c>
       <c r="E33" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1174,15 +1174,37 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>91854</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2484</v>
+      </c>
+      <c r="E34" t="n">
+        <v>398</v>
+      </c>
+      <c r="F34" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>263844</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D35" t="n">
         <v>4304</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E35" t="n">
         <v>698</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
         <v>20</v>
       </c>
     </row>

--- a/output/roomself_excel/13044.xlsx
+++ b/output/roomself_excel/13044.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,15 @@
       <c r="D2" t="n">
         <v>1132</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +535,23 @@
       <c r="D3" t="n">
         <v>2368</v>
       </c>
-      <c r="E3" t="n">
-        <v>347</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +568,23 @@
       <c r="D4" t="n">
         <v>3884</v>
       </c>
-      <c r="E4" t="n">
-        <v>20</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
         <v>19</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +601,31 @@
       <c r="D5" t="n">
         <v>4556</v>
       </c>
-      <c r="E5" t="n">
-        <v>1000</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>596</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +642,38 @@
       <c r="D6" t="n">
         <v>6436</v>
       </c>
-      <c r="E6" t="n">
-        <v>1008</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>661</v>
+        <v>486</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>557</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>258</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +691,31 @@
       <c r="D7" t="n">
         <v>3328</v>
       </c>
-      <c r="E7" t="n">
-        <v>482</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>390</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>370</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +732,15 @@
       <c r="D8" t="n">
         <v>1856</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +757,23 @@
       <c r="D9" t="n">
         <v>2872</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>327</v>
       </c>
-      <c r="F9" t="n">
-        <v>20</v>
-      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,15 @@
       <c r="D10" t="n">
         <v>1084</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +815,15 @@
       <c r="D11" t="n">
         <v>928</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +840,23 @@
       <c r="D12" t="n">
         <v>3960</v>
       </c>
-      <c r="E12" t="n">
-        <v>507</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +873,38 @@
       <c r="D13" t="n">
         <v>7800</v>
       </c>
-      <c r="E13" t="n">
-        <v>1009</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>703</v>
+        <v>683</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>159</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>970</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +922,15 @@
       <c r="D14" t="n">
         <v>2320</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +947,31 @@
       <c r="D15" t="n">
         <v>5620</v>
       </c>
-      <c r="E15" t="n">
-        <v>1012</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>453</v>
-      </c>
+        <v>972</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>866</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +988,23 @@
       <c r="D16" t="n">
         <v>5532</v>
       </c>
-      <c r="E16" t="n">
-        <v>1012</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>411</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1021,31 @@
       <c r="D17" t="n">
         <v>7472</v>
       </c>
-      <c r="E17" t="n">
-        <v>1516</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>412</v>
-      </c>
+        <v>1476</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>784</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1062,31 @@
       <c r="D18" t="n">
         <v>4368</v>
       </c>
-      <c r="E18" t="n">
-        <v>707</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>425</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>405</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1103,23 @@
       <c r="D19" t="n">
         <v>3056</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>254</v>
       </c>
-      <c r="F19" t="n">
-        <v>20</v>
-      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1136,31 @@
       <c r="D20" t="n">
         <v>62768</v>
       </c>
-      <c r="E20" t="n">
-        <v>12425</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>3078</v>
-      </c>
+        <v>22282</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3038</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1177,23 @@
       <c r="D21" t="n">
         <v>3420</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>581</v>
       </c>
-      <c r="F21" t="n">
-        <v>20</v>
-      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1210,15 @@
       <c r="D22" t="n">
         <v>3896</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1235,15 @@
       <c r="D23" t="n">
         <v>2920</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1260,15 @@
       <c r="D24" t="n">
         <v>1344</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1285,23 @@
       <c r="D25" t="n">
         <v>3768</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>484</v>
       </c>
-      <c r="F25" t="n">
-        <v>20</v>
-      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1318,15 @@
       <c r="D26" t="n">
         <v>3484</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1343,23 @@
       <c r="D27" t="n">
         <v>8696</v>
       </c>
-      <c r="E27" t="n">
-        <v>932</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>293</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1376,15 @@
       <c r="D28" t="n">
         <v>2740</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1401,15 @@
       <c r="D29" t="n">
         <v>1140</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1426,15 @@
       <c r="D30" t="n">
         <v>896</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1451,15 @@
       <c r="D31" t="n">
         <v>1285</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1476,15 @@
       <c r="D32" t="n">
         <v>2956</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1501,15 @@
       <c r="D33" t="n">
         <v>1088</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1526,31 @@
       <c r="D34" t="n">
         <v>2484</v>
       </c>
-      <c r="E34" t="n">
-        <v>398</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>263</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>243</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1567,23 @@
       <c r="D35" t="n">
         <v>4304</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>698</v>
       </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/13044.xlsx
+++ b/output/roomself_excel/13044.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,46 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -519,6 +559,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -552,6 +600,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +641,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -626,6 +690,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -675,6 +747,14 @@
       <c r="M6" t="n">
         <v>20</v>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -716,6 +796,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -741,6 +829,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -774,6 +870,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -799,6 +903,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -824,6 +936,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -857,6 +977,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -906,6 +1034,14 @@
       <c r="M13" t="n">
         <v>20</v>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -931,6 +1067,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -972,6 +1116,38 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>95</v>
+      </c>
+      <c r="U15" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1181,26 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1046,6 +1242,26 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1087,6 +1303,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1120,6 +1344,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1161,6 +1393,38 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2705</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>1836</v>
+      </c>
+      <c r="U20" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1194,6 +1458,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1219,6 +1491,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1244,6 +1524,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1269,6 +1557,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1302,6 +1598,26 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>20</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1327,6 +1643,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1360,6 +1684,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1385,6 +1717,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1410,6 +1750,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1435,6 +1783,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1460,6 +1816,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1485,6 +1849,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1510,6 +1882,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1551,6 +1931,26 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1584,6 +1984,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
